--- a/mapping_data/DifficultWords/BU_A.xlsx
+++ b/mapping_data/DifficultWords/BU_A.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
   <si>
     <t xml:space="preserve"> Big5 區段</t>
   </si>
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Unicode 字形</t>
   </si>
   <si>
-    <t xml:space="preserve">使用者造字區：第一段</t>
+    <t xml:space="preserve">使用者造字區</t>
   </si>
   <si>
     <t xml:space="preserve">FAD7</t>
@@ -107,6 +107,15 @@
   </si>
   <si>
     <t xml:space="preserve">卉</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FA41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46E5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">䛥</t>
   </si>
 </sst>
 </file>
@@ -146,9 +155,9 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="新細明體"/>
       <family val="2"/>
-      <charset val="1"/>
+      <charset val="136"/>
     </font>
     <font>
       <sz val="8"/>
@@ -212,33 +221,37 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -497,7 +510,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="32.08"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="16.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="16.02"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="2" width="8.53"/>
   </cols>
   <sheetData>
@@ -620,8 +633,25 @@
         <v>28</v>
       </c>
     </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="0"/>
+      <c r="C10" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
